--- a/Result/profitability/2409.xlsx
+++ b/Result/profitability/2409.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.53125</v>
+        <v>0.56875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.97375</v>
+        <v>13.24625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>0.86625</v>
+        <v>0.8625</v>
       </c>
       <c r="N3" t="n">
-        <v>14.735</v>
+        <v>15.375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.85125</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>14.7475</v>
+        <v>14.85625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-3.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4075</v>
+        <v>0.3974999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.84625</v>
+        <v>8.787500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07624999999999993</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2375</v>
+        <v>3.6725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.002500000000000099</v>
+        <v>-0.02750000000000008</v>
       </c>
       <c r="N7" t="n">
-        <v>2.21375</v>
+        <v>2.50375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0537499999999999</v>
+        <v>0.09499999999999992</v>
       </c>
       <c r="N8" t="n">
-        <v>2.33875</v>
+        <v>2.48875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.79</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02625000000000011</v>
+        <v>-0.02625000000000008</v>
       </c>
       <c r="N9" t="n">
         <v>1.81125</v>
@@ -1648,7 +1648,7 @@
         <v>-0.3525000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01749999999999963</v>
+        <v>0.01750000000000007</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>70891</v>
+      </c>
+      <c r="D75" t="n">
+        <v>61643</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9248</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>218</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2533</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2751</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1274999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.2125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.200000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1012658227848102</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3076923076923077</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4699999999999989</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03476331360946738</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
